--- a/shopping.xlsx
+++ b/shopping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/da5d670e915d56ad/Documents/_Personnel/_Travaux/Spy turtle/spy_turtle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="324" documentId="8_{35EEAFD2-E8FE-4A41-A491-6945E7574AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5057E631-699D-4069-B08D-C006CD380208}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="8_{35EEAFD2-E8FE-4A41-A491-6945E7574AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6AFA6F-CAA9-408F-9B39-E747A280FFD9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{075D985D-50BF-4E50-8104-7E4D414F1B02}"/>
   </bookViews>
@@ -707,8 +707,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" width="16.36328125" customWidth="1"/>
-    <col min="8" max="8" width="31.7265625" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" customWidth="1"/>
+    <col min="9" max="9" width="31" customWidth="1"/>
     <col min="10" max="10" width="18.90625" customWidth="1"/>
     <col min="11" max="11" width="48.26953125" customWidth="1"/>
     <col min="12" max="12" width="26.90625" customWidth="1"/>

--- a/shopping.xlsx
+++ b/shopping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/da5d670e915d56ad/Documents/_Personnel/_Travaux/Spy turtle/spy_turtle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="8_{35EEAFD2-E8FE-4A41-A491-6945E7574AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6AFA6F-CAA9-408F-9B39-E747A280FFD9}"/>
+  <xr:revisionPtr revIDLastSave="328" documentId="8_{35EEAFD2-E8FE-4A41-A491-6945E7574AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B64576E5-E9BE-4291-AD58-43A003AA3FA5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{075D985D-50BF-4E50-8104-7E4D414F1B02}"/>
   </bookViews>
